--- a/IWAI-2026-assignments.xlsx
+++ b/IWAI-2026-assignments.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
   <si>
     <t xml:space="preserve">pap_number</t>
   </si>
@@ -34,52 +34,40 @@
     <t xml:space="preserve">pap_authors</t>
   </si>
   <si>
-    <t xml:space="preserve">pap_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pap_stream</t>
-  </si>
-  <si>
     <t xml:space="preserve">rev_id</t>
   </si>
   <si>
-    <t xml:space="preserve">score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rev_role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rev_tasks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rev_nsubm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rev_streams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rev_types</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rev_submis</t>
-  </si>
-  <si>
     <t xml:space="preserve">zqV2uduW5y</t>
   </si>
   <si>
-    <t xml:space="preserve">Tim Riddhi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">poster</t>
+    <t xml:space="preserve">Active Inference as the Reasoning layer for Physical AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Verbelen, Toon Van de Maele, Corrado Pezzato, Riddhi J. Pitliya</t>
   </si>
   <si>
     <t xml:space="preserve">~Ivilin_Peev_Stoianov1</t>
   </si>
   <si>
-    <t xml:space="preserve">~Daria_de_Tinguy1</t>
+    <t xml:space="preserve">~Ivilin_Stoianov1</t>
   </si>
   <si>
     <t xml:space="preserve">zEx1niIMY0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online Generalised Predictive Coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mehran Hossein Zadeh Bazargani, Szymon Urbas, Adeel Razi, Thomas Brendan Murphy, Karl Friston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EUoove9wtH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Inference of Social Exclusion: Computational Modelling of Cyberball in Borderline Personality Disorder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefano Ventre, Rodolfo Rossi, Jialin Shi, Paolo Ossola</t>
   </si>
 </sst>
 </file>
@@ -176,7 +164,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -186,6 +174,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -199,6 +191,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -226,133 +222,125 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="20.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="52.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="99.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="26.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>17</v>
-      </c>
+      <c r="B2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
+      <c r="B3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="6" t="s">
-        <v>18</v>
+      <c r="B5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
